--- a/map/railway/nodes.xlsx
+++ b/map/railway/nodes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Unida\Documents\VSC\Python\EpidemicSimulation\map\railway\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2456E029-21B7-45CD-963F-455AB9198884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8E8A76-3879-437C-A053-182F759A039C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75C1F7D0-F845-4A32-83A6-97DD4D1488C1}"/>
+    <workbookView xWindow="825" yWindow="825" windowWidth="21600" windowHeight="11100" xr2:uid="{75C1F7D0-F845-4A32-83A6-97DD4D1488C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -247,13 +247,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -722,46 +722,46 @@
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="A15" s="6">
         <v>165</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="A16" s="6">
         <v>312</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="A17" s="6">
         <v>329</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="A18" s="6">
         <v>350</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>45</v>
       </c>
     </row>
